--- a/bts-gpme/tp-1083/ressources/R06_Creances_clients_tresorerie_et_solutions.xlsx
+++ b/bts-gpme/tp-1083/ressources/R06_Creances_clients_tresorerie_et_solutions.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Creances_B2B" sheetId="1" r:id="Raabd3fd7f15e4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tresorerie_8_semaines" sheetId="2" r:id="R62a86daa7a474446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solutions_financement" sheetId="3" r:id="R7849a457e00c48ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Creances_B2B" sheetId="1" r:id="Rf346af1d631d4198"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tresorerie_8_semaines" sheetId="2" r:id="Ra5d7640325d749ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solutions_financement" sheetId="3" r:id="R452586f83eb04cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle_creances" sheetId="4" r:id="Rfc57dad61f9f419f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +21,7 @@
     <x:numFmt numFmtId="201" formatCode="#,##0.00 &quot;€&quot;"/>
     <x:numFmt numFmtId="202" formatCode="#,##0 &quot;€&quot;"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,8 +38,24 @@
       <x:color rgb="FF173F45"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6A4A00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF24495A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF244E2E"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +77,31 @@
         <x:fgColor rgb="FFE8F3E8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEFF2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F3E8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -68,7 +110,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="58">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -134,6 +176,56 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1054,7 +1146,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9ac38b04944cd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01ab0f3f9bbd42db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1087,7 +1179,20 @@
       <x:c r="H1"/>
       <x:c r="I1"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Les encaissements B2B de ce budget sont des prévisions agrégées de flux : ils ne correspondent pas ligne à ligne aux factures de l’onglet « Creances_B2B ».</x:v>
+      </x:c>
+      <x:c r="B2" s="52"/>
+      <x:c r="C2" s="52"/>
+      <x:c r="D2" s="52"/>
+      <x:c r="E2" s="52"/>
+      <x:c r="F2" s="52"/>
+      <x:c r="G2" s="52"/>
+      <x:c r="H2" s="52"/>
+      <x:c r="I2" s="52"/>
+    </x:row>
+    <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="14" t="str">
         <x:v>Semaine</x:v>
       </x:c>
@@ -1116,7 +1221,7 @@
         <x:v>Trésorerie fin - scénario prudent</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="20" t="str">
         <x:v>S40</x:v>
       </x:c>
@@ -1141,7 +1246,7 @@
       <x:c r="H4" s="28"/>
       <x:c r="I4" s="28"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="20" t="str">
         <x:v>S41</x:v>
       </x:c>
@@ -1164,7 +1269,7 @@
       <x:c r="H5" s="28"/>
       <x:c r="I5" s="28"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="20" t="str">
         <x:v>S42</x:v>
       </x:c>
@@ -1187,7 +1292,7 @@
       <x:c r="H6" s="28"/>
       <x:c r="I6" s="28"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="20" t="str">
         <x:v>S43</x:v>
       </x:c>
@@ -1210,7 +1315,7 @@
       <x:c r="H7" s="28"/>
       <x:c r="I7" s="28"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="20" t="str">
         <x:v>S44</x:v>
       </x:c>
@@ -1233,7 +1338,7 @@
       <x:c r="H8" s="28"/>
       <x:c r="I8" s="28"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="20" t="str">
         <x:v>S45</x:v>
       </x:c>
@@ -1256,7 +1361,7 @@
       <x:c r="H9" s="28"/>
       <x:c r="I9" s="28"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="20" t="str">
         <x:v>S46</x:v>
       </x:c>
@@ -1279,7 +1384,7 @@
       <x:c r="H10" s="28"/>
       <x:c r="I10" s="28"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:v>S47</x:v>
       </x:c>
@@ -1302,10 +1407,18 @@
       <x:c r="H11" s="28"/>
       <x:c r="I11" s="28"/>
     </x:row>
-    <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="32" t="str">
-        <x:v>À faire : 1) Construire le scénario nominal en chaînant les soldes. 2) Construire un scénario prudent dans lequel 60 % seulement des encaissements B2B de S40 à S43 sont reçus à la date prévue et le solde est reporté de 3 semaines ; les encaissements B2C restent inchangés. 3) Repérer la première semaine de tension et proposer des solutions adaptées.</x:v>
-      </x:c>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="57" t="str">
+        <x:v>À faire : 1) Construire le scénario nominal en chaînant les soldes. 2) Construire le scénario prudent : pour S40 à S43, 60 % des encaissements B2B sont reçus à la date prévue et les 40 % restants sont reportés exactement 3 semaines plus tard (ils ne disparaissent pas). 3) Repérer la première semaine sous la réserve minimale de 60 000 €, le point bas de trésorerie et le montant nécessaire pour rétablir cette réserve. 4) Proposer des solutions adaptées.</x:v>
+      </x:c>
+      <x:c r="B13" s="57"/>
+      <x:c r="C13" s="57"/>
+      <x:c r="D13" s="57"/>
+      <x:c r="E13" s="57"/>
+      <x:c r="F13" s="57"/>
+      <x:c r="G13" s="57"/>
+      <x:c r="H13" s="57"/>
+      <x:c r="I13" s="57"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1"/>
     <x:row r="15" ht="24" customHeight="1"/>
@@ -1313,7 +1426,8 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A13:I16"/>
+    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A13:I13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1343,6 +1457,17 @@
       <x:c r="F1"/>
       <x:c r="G1"/>
     </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Comparez chaque solution selon le besoin auquel elle répond : prévenir/réduire l’exposition, transférer une partie du risque d’impayé et/ou financer le besoin de trésorerie. Vérifiez toujours les conditions d’éligibilité et les exclusions.</x:v>
+      </x:c>
+      <x:c r="B2" s="52"/>
+      <x:c r="C2" s="52"/>
+      <x:c r="D2" s="52"/>
+      <x:c r="E2" s="52"/>
+      <x:c r="F2" s="52"/>
+      <x:c r="G2" s="52"/>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
         <x:v>Solution</x:v>
@@ -1484,10 +1609,191 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220e69083af140f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65273e75e82d421f"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="38" t="str">
+        <x:v>CONTRÔLE DES CRÉANCES — ne modifiez ou ne supprimez aucune donnée source sans conserver la trace du contrôle.</x:v>
+      </x:c>
+      <x:c r="B1" s="38"/>
+      <x:c r="C1" s="38"/>
+      <x:c r="D1" s="38"/>
+      <x:c r="E1" s="38"/>
+      <x:c r="F1" s="38"/>
+      <x:c r="G1" s="38"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="42" t="str">
+        <x:v>Date d’analyse : 30/09/2026. Un doublon ou une incohérence apparente reste « à confirmer » tant qu’une pièce ou une personne habilitée ne permet pas de trancher.</x:v>
+      </x:c>
+      <x:c r="B2" s="42"/>
+      <x:c r="C2" s="42"/>
+      <x:c r="D2" s="42"/>
+      <x:c r="E2" s="42"/>
+      <x:c r="F2" s="42"/>
+      <x:c r="G2" s="42"/>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="47" t="str">
+        <x:v>Facture / ligne</x:v>
+      </x:c>
+      <x:c r="B4" s="47" t="str">
+        <x:v>Point contrôlé / anomalie</x:v>
+      </x:c>
+      <x:c r="C4" s="47" t="str">
+        <x:v>Fait constaté</x:v>
+      </x:c>
+      <x:c r="D4" s="47" t="str">
+        <x:v>Statut du contrôle</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="str">
+        <x:v>Retraitement proposé</x:v>
+      </x:c>
+      <x:c r="F4" s="47" t="str">
+        <x:v>Justification</x:v>
+      </x:c>
+      <x:c r="G4" s="47" t="str">
+        <x:v>Information à confirmer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="48"/>
+      <x:c r="B5" s="48"/>
+      <x:c r="C5" s="48"/>
+      <x:c r="D5" s="48"/>
+      <x:c r="E5" s="48"/>
+      <x:c r="F5" s="48"/>
+      <x:c r="G5" s="48"/>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
+      <x:c r="A6" s="48"/>
+      <x:c r="B6" s="48"/>
+      <x:c r="C6" s="48"/>
+      <x:c r="D6" s="48"/>
+      <x:c r="E6" s="48"/>
+      <x:c r="F6" s="48"/>
+      <x:c r="G6" s="48"/>
+    </x:row>
+    <x:row r="7" ht="44" customHeight="1">
+      <x:c r="A7" s="48"/>
+      <x:c r="B7" s="48"/>
+      <x:c r="C7" s="48"/>
+      <x:c r="D7" s="48"/>
+      <x:c r="E7" s="48"/>
+      <x:c r="F7" s="48"/>
+      <x:c r="G7" s="48"/>
+    </x:row>
+    <x:row r="8" ht="44" customHeight="1">
+      <x:c r="A8" s="48"/>
+      <x:c r="B8" s="48"/>
+      <x:c r="C8" s="48"/>
+      <x:c r="D8" s="48"/>
+      <x:c r="E8" s="48"/>
+      <x:c r="F8" s="48"/>
+      <x:c r="G8" s="48"/>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
+      <x:c r="A9" s="48"/>
+      <x:c r="B9" s="48"/>
+      <x:c r="C9" s="48"/>
+      <x:c r="D9" s="48"/>
+      <x:c r="E9" s="48"/>
+      <x:c r="F9" s="48"/>
+      <x:c r="G9" s="48"/>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
+      <x:c r="A10" s="48"/>
+      <x:c r="B10" s="48"/>
+      <x:c r="C10" s="48"/>
+      <x:c r="D10" s="48"/>
+      <x:c r="E10" s="48"/>
+      <x:c r="F10" s="48"/>
+      <x:c r="G10" s="48"/>
+    </x:row>
+    <x:row r="11" ht="44" customHeight="1">
+      <x:c r="A11" s="48"/>
+      <x:c r="B11" s="48"/>
+      <x:c r="C11" s="48"/>
+      <x:c r="D11" s="48"/>
+      <x:c r="E11" s="48"/>
+      <x:c r="F11" s="48"/>
+      <x:c r="G11" s="48"/>
+    </x:row>
+    <x:row r="12" ht="44" customHeight="1">
+      <x:c r="A12" s="48"/>
+      <x:c r="B12" s="48"/>
+      <x:c r="C12" s="48"/>
+      <x:c r="D12" s="48"/>
+      <x:c r="E12" s="48"/>
+      <x:c r="F12" s="48"/>
+      <x:c r="G12" s="48"/>
+    </x:row>
+    <x:row r="13" ht="44" customHeight="1">
+      <x:c r="A13" s="48"/>
+      <x:c r="B13" s="48"/>
+      <x:c r="C13" s="48"/>
+      <x:c r="D13" s="48"/>
+      <x:c r="E13" s="48"/>
+      <x:c r="F13" s="48"/>
+      <x:c r="G13" s="48"/>
+    </x:row>
+    <x:row r="14" ht="44" customHeight="1">
+      <x:c r="A14" s="48"/>
+      <x:c r="B14" s="48"/>
+      <x:c r="C14" s="48"/>
+      <x:c r="D14" s="48"/>
+      <x:c r="E14" s="48"/>
+      <x:c r="F14" s="48"/>
+      <x:c r="G14" s="48"/>
+    </x:row>
+    <x:row r="15" ht="44" customHeight="1">
+      <x:c r="A15" s="48"/>
+      <x:c r="B15" s="48"/>
+      <x:c r="C15" s="48"/>
+      <x:c r="D15" s="48"/>
+      <x:c r="E15" s="48"/>
+      <x:c r="F15" s="48"/>
+      <x:c r="G15" s="48"/>
+    </x:row>
+    <x:row r="16" ht="44" customHeight="1">
+      <x:c r="A16" s="48"/>
+      <x:c r="B16" s="48"/>
+      <x:c r="C16" s="48"/>
+      <x:c r="D16" s="48"/>
+      <x:c r="E16" s="48"/>
+      <x:c r="F16" s="48"/>
+      <x:c r="G16" s="48"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D16">
+      <x:formula1>"Conforme,À vérifier,Anomalie probable,À confirmer"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>